--- a/Result/profitability/1210.xlsx
+++ b/Result/profitability/1210.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.96</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.00125</v>
       </c>
       <c r="N2" t="n">
-        <v>13.9475</v>
+        <v>13.825</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.71</v>
       </c>
       <c r="M3" t="n">
-        <v>1.02375</v>
+        <v>0.9325</v>
       </c>
       <c r="N3" t="n">
-        <v>13.35125</v>
+        <v>13.1775</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9525</v>
+        <v>0.8875</v>
       </c>
       <c r="N4" t="n">
-        <v>12.29125</v>
+        <v>12.03625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.14</v>
       </c>
       <c r="M5" t="n">
-        <v>0.80375</v>
+        <v>0.7849999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>11.2025</v>
+        <v>11.245</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.09</v>
       </c>
       <c r="M6" t="n">
-        <v>0.855</v>
+        <v>0.8049999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>11.05625</v>
+        <v>10.86875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.78</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8362499999999999</v>
+        <v>0.695</v>
       </c>
       <c r="N7" t="n">
-        <v>10.5525</v>
+        <v>10.2925</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,13 +1391,13 @@
         <v>0.63</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7074999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="N8" t="n">
-        <v>9.754999999999999</v>
+        <v>9.665000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>0.56125</v>
       </c>
       <c r="N10" t="n">
-        <v>8.856249999999999</v>
+        <v>8.856250000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.84</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5287499999999999</v>
+        <v>0.5287500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>9.1325</v>
@@ -2029,7 +2029,7 @@
         <v>0.63375</v>
       </c>
       <c r="N13" t="n">
-        <v>9.395000000000001</v>
+        <v>9.395</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>26965</v>
+      </c>
+      <c r="D75" t="n">
+        <v>23366</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3599</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="G75" t="n">
+        <v>914</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.39%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J75" t="n">
+        <v>897</v>
+      </c>
+      <c r="K75" t="n">
+        <v>447</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.00625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.39625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.4099999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4361702127659574</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.7200000000000006</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05117270788912587</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.2205882352941176</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.3399999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.02613374327440421</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
